--- a/data/trans_dic/P34B04_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P34B04_R-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza algún entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares, 3 veces por semana o más</t>
+          <t>Población que realiza algún entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,13</t>
+          <t>5,05; 8,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 7,38</t>
+          <t>3,87; 7,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 9,43</t>
+          <t>4,25; 9,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,14</t>
+          <t>0,38; 2,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,75</t>
+          <t>0,27; 1,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,31</t>
+          <t>0,28; 1,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 4,98</t>
+          <t>2,95; 4,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,21</t>
+          <t>2,32; 4,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 4,74</t>
+          <t>2,45; 5,05</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,35; 8,61</t>
+          <t>5,45; 8,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 6,92</t>
+          <t>3,88; 6,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 11,14</t>
+          <t>3,85; 11,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,52</t>
+          <t>0,32; 1,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,11</t>
+          <t>0,72; 2,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,43</t>
+          <t>1,59; 3,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 4,75</t>
+          <t>3,0; 4,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,13</t>
+          <t>2,49; 4,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 6,88</t>
+          <t>3,44; 6,98</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 10,53</t>
+          <t>6,57; 10,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,5; 8,45</t>
+          <t>4,64; 8,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 11,68</t>
+          <t>5,16; 10,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,31</t>
+          <t>0,13; 1,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,74</t>
+          <t>0,36; 1,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,85</t>
+          <t>0,63; 2,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,58</t>
+          <t>3,36; 5,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,61</t>
+          <t>2,61; 4,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,87</t>
+          <t>2,51; 5,75</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,33; 9,68</t>
+          <t>6,26; 9,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,5; 10,01</t>
+          <t>6,52; 10,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,41; 14,32</t>
+          <t>8,21; 13,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,87</t>
+          <t>0,43; 1,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,73</t>
+          <t>1,11; 2,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,81</t>
+          <t>0,95; 2,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,31; 5,07</t>
+          <t>3,32; 5,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,97; 5,86</t>
+          <t>3,98; 5,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 7,33</t>
+          <t>4,61; 7,52</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,56; 8,35</t>
+          <t>6,55; 8,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,55; 7,22</t>
+          <t>5,51; 7,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 9,71</t>
+          <t>6,44; 9,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,14</t>
+          <t>0,51; 1,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,67</t>
+          <t>0,95; 1,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,13</t>
+          <t>1,22; 2,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,56</t>
+          <t>3,52; 4,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 4,22</t>
+          <t>3,3; 4,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,06; 5,6</t>
+          <t>4,11; 5,64</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza algún entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares, 3 veces por semana o más</t>
+          <t>Población que realiza algún entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>37003; 64107</t>
+          <t>35486; 63079</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26420; 49793</t>
+          <t>26136; 50191</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27659; 59827</t>
+          <t>26972; 59028</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1917; 14939</t>
+          <t>2647; 15168</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1847; 11792</t>
+          <t>1832; 11653</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2055; 8848</t>
+          <t>1872; 9362</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40975; 69748</t>
+          <t>41343; 69597</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31777; 56731</t>
+          <t>31211; 55085</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31364; 62047</t>
+          <t>32051; 66021</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54429; 87655</t>
+          <t>55483; 90687</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40855; 70715</t>
+          <t>39625; 69427</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49623; 132855</t>
+          <t>45977; 133976</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3994; 15616</t>
+          <t>3326; 15626</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7626; 21963</t>
+          <t>7561; 21649</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14217; 32851</t>
+          <t>15205; 34159</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61153; 97319</t>
+          <t>61411; 96056</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52469; 85312</t>
+          <t>51516; 87804</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>74931; 147845</t>
+          <t>73945; 150090</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>47991; 79766</t>
+          <t>49805; 82454</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34173; 64157</t>
+          <t>35268; 62388</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36179; 82280</t>
+          <t>36355; 75822</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>989; 10158</t>
+          <t>996; 9031</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2876; 13644</t>
+          <t>2812; 13672</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6884; 26634</t>
+          <t>5923; 26513</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52043; 85616</t>
+          <t>51576; 85492</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>41585; 71245</t>
+          <t>40324; 71864</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>41766; 96104</t>
+          <t>41034; 94265</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59919; 91655</t>
+          <t>59260; 91245</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60918; 93849</t>
+          <t>61162; 94741</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77952; 132735</t>
+          <t>76086; 126403</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3839; 19644</t>
+          <t>4493; 19997</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11276; 28480</t>
+          <t>11553; 28610</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11223; 30666</t>
+          <t>10318; 28571</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66144; 101267</t>
+          <t>66373; 101255</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>78630; 116116</t>
+          <t>78903; 116521</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93385; 147971</t>
+          <t>92964; 151752</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>224671; 286021</t>
+          <t>224157; 285987</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>188244; 245235</t>
+          <t>187002; 245684</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>224525; 335682</t>
+          <t>222724; 334839</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18256; 40677</t>
+          <t>18211; 41107</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32736; 59222</t>
+          <t>33511; 58462</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>45189; 77880</t>
+          <t>44685; 78759</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>249277; 318599</t>
+          <t>245520; 317842</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>230891; 292819</t>
+          <t>229156; 296573</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>288626; 398663</t>
+          <t>292302; 400992</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34B04_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P34B04_R-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,32 +678,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,05; 8,98</t>
+          <t>4,97; 8,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,87; 7,44</t>
+          <t>4,0; 7,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 9,3</t>
+          <t>4,36; 9,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,18</t>
+          <t>0,38; 2,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,73</t>
+          <t>0,28; 1,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,39</t>
+          <t>0,31; 1,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,09</t>
+          <t>2,31; 4,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,05</t>
+          <t>2,4; 4,69</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 8,91</t>
+          <t>5,33; 8,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 6,79</t>
+          <t>3,97; 7,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 11,23</t>
+          <t>7,82; 12,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,52</t>
+          <t>0,39; 1,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,08</t>
+          <t>0,73; 2,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,57</t>
+          <t>1,53; 3,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 4,69</t>
+          <t>3,0; 4,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,25</t>
+          <t>2,49; 4,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,98</t>
+          <t>4,95; 7,8</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,57; 10,88</t>
+          <t>6,48; 10,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 8,21</t>
+          <t>4,52; 8,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,16; 10,76</t>
+          <t>5,02; 10,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,16</t>
+          <t>0,13; 1,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,74</t>
+          <t>0,38; 1,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,84</t>
+          <t>1,37; 4,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 5,57</t>
+          <t>3,39; 5,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 4,65</t>
+          <t>2,69; 4,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,75</t>
+          <t>3,71; 6,65</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,26; 9,64</t>
+          <t>6,17; 9,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,52; 10,11</t>
+          <t>6,45; 10,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,21; 13,64</t>
+          <t>8,24; 13,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,9</t>
+          <t>0,36; 1,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,74</t>
+          <t>1,16; 2,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,62</t>
+          <t>1,1; 2,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 5,07</t>
+          <t>3,23; 5,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 5,88</t>
+          <t>3,95; 5,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 7,52</t>
+          <t>4,81; 7,39</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,55; 8,35</t>
+          <t>6,61; 8,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,51; 7,24</t>
+          <t>5,54; 7,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,44; 9,68</t>
+          <t>7,77; 10,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,16</t>
+          <t>0,5; 1,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,65</t>
+          <t>0,94; 1,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,15</t>
+          <t>1,44; 2,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 4,55</t>
+          <t>3,57; 4,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,3; 4,27</t>
+          <t>3,3; 4,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 5,64</t>
+          <t>4,66; 5,99</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39793</t>
+          <t>43135</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44169</t>
+          <t>47966</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35486; 63079</t>
+          <t>34888; 60856</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26136; 50191</t>
+          <t>26976; 50759</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26972; 59028</t>
+          <t>30083; 62377</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2647; 15168</t>
+          <t>2642; 14370</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1832; 11653</t>
+          <t>1854; 10980</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1872; 9362</t>
+          <t>2298; 9753</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41343; 69597</t>
+          <t>41323; 69514</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31211; 55085</t>
+          <t>31083; 55877</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32051; 66021</t>
+          <t>34103; 66641</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94455</t>
+          <t>106954</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22485</t>
+          <t>24216</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>116940</t>
+          <t>131170</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55483; 90687</t>
+          <t>54226; 87861</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39625; 69427</t>
+          <t>40553; 71758</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45977; 133976</t>
+          <t>82053; 132724</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3326; 15626</t>
+          <t>4056; 15794</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7561; 21649</t>
+          <t>7635; 21662</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15205; 34159</t>
+          <t>16328; 35105</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61411; 96056</t>
+          <t>61536; 97260</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51516; 87804</t>
+          <t>51411; 85624</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>73945; 150090</t>
+          <t>104913; 165293</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52688</t>
+          <t>60138</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15510</t>
+          <t>19086</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>68198</t>
+          <t>79224</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>49805; 82454</t>
+          <t>49117; 80722</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35268; 62388</t>
+          <t>34361; 61840</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36355; 75822</t>
+          <t>40305; 81625</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>996; 9031</t>
+          <t>996; 9940</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2812; 13672</t>
+          <t>2989; 14242</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5923; 26513</t>
+          <t>11141; 33500</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51576; 85492</t>
+          <t>52008; 86793</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>40324; 71864</t>
+          <t>41584; 71352</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>41034; 94265</t>
+          <t>59871; 107457</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100466</t>
+          <t>104918</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17892</t>
+          <t>19793</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>118358</t>
+          <t>124712</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59260; 91245</t>
+          <t>58397; 90642</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>61162; 94741</t>
+          <t>60506; 96040</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>76086; 126403</t>
+          <t>81500; 129498</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4493; 19997</t>
+          <t>3774; 17781</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11553; 28610</t>
+          <t>12077; 29135</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10318; 28571</t>
+          <t>12244; 31070</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66373; 101255</t>
+          <t>64497; 100049</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>78903; 116521</t>
+          <t>78177; 118351</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>92964; 151752</t>
+          <t>101208; 155507</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>287401</t>
+          <t>315145</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60263</t>
+          <t>67927</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>347664</t>
+          <t>383072</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>224157; 285987</t>
+          <t>226287; 287613</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>187002; 245684</t>
+          <t>187975; 243386</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>222724; 334839</t>
+          <t>274244; 360886</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18211; 41107</t>
+          <t>17891; 41586</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>33511; 58462</t>
+          <t>33294; 58771</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44685; 78759</t>
+          <t>53587; 86655</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>245520; 317842</t>
+          <t>248887; 315449</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>229156; 296573</t>
+          <t>229198; 293767</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>292302; 400992</t>
+          <t>338497; 435086</t>
         </is>
       </c>
     </row>
